--- a/test.xlsx
+++ b/test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nben1\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nben1\Desktop\vjanjo\vyanjo-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{969006F4-2809-4C1E-B719-69338F1099B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A5146D-FA71-4630-83FF-EF6AB56F9EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4F1481FF-A345-401B-B58B-F3878D4DE571}"/>
   </bookViews>
@@ -38,6 +38,33 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>1 Day</t>
+  </si>
+  <si>
+    <t>3 Days</t>
+  </si>
+  <si>
+    <t>1 Week</t>
+  </si>
+  <si>
+    <t>2 Weeks</t>
+  </si>
+  <si>
+    <t>1 Month</t>
+  </si>
+  <si>
+    <t>Non Veg</t>
+  </si>
+  <si>
+    <t>249+299</t>
+  </si>
+  <si>
+    <t>739+759</t>
+  </si>
+  <si>
     <t>Plan</t>
   </si>
   <si>
@@ -50,75 +77,56 @@
     <t>Tiffin</t>
   </si>
   <si>
+    <t>Lunch (normal price + special price)</t>
+  </si>
+  <si>
     <t>Dinner</t>
   </si>
   <si>
+    <t>Tiffin+lunch (normal price + special price)</t>
+  </si>
+  <si>
     <t>Tiffin+Dinner</t>
   </si>
   <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>Veg</t>
-  </si>
-  <si>
-    <t>1 Day</t>
-  </si>
-  <si>
-    <t>89+129</t>
-  </si>
-  <si>
-    <t>149+219</t>
-  </si>
-  <si>
-    <t>169+199</t>
-  </si>
-  <si>
-    <t>229+299</t>
-  </si>
-  <si>
-    <t>3 Days</t>
-  </si>
-  <si>
-    <t>265+305</t>
-  </si>
-  <si>
-    <t>459+559</t>
-  </si>
-  <si>
-    <t>549+599</t>
-  </si>
-  <si>
-    <t>679+719</t>
-  </si>
-  <si>
-    <t>1 Week</t>
-  </si>
-  <si>
-    <t>2 Weeks</t>
-  </si>
-  <si>
-    <t>1 Month</t>
-  </si>
-  <si>
-    <t>Lunch normal price + special price</t>
-  </si>
-  <si>
-    <t>Tiffin+lunch normal price + special price</t>
-  </si>
-  <si>
-    <t>Lunch+Dinner normal price + special price</t>
-  </si>
-  <si>
-    <t>Full Meal normal price + special price</t>
+    <t>Lunch+Dinner (normal price + special price)</t>
+  </si>
+  <si>
+    <t>Full Meal (normal price + special price)</t>
+  </si>
+  <si>
+    <t>109+129</t>
+  </si>
+  <si>
+    <t>169+219</t>
+  </si>
+  <si>
+    <t>189+219</t>
+  </si>
+  <si>
+    <t>325+345</t>
+  </si>
+  <si>
+    <t>519+599</t>
+  </si>
+  <si>
+    <t>609+639</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -146,10 +154,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,205 +502,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A8CC5D-3F41-43AF-9FF4-652D5EC4DE70}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultColWidth="18.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="16384" width="18.7265625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E2" s="4">
+        <v>69</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4">
+        <v>99</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="4">
+        <v>149</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E3" s="4">
+        <v>205</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4">
+        <v>295</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="4">
+        <v>499</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E4" s="4">
+        <v>469</v>
+      </c>
+      <c r="G4" s="4">
+        <v>829</v>
+      </c>
+      <c r="I4" s="4">
+        <v>679</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1299</v>
+      </c>
+      <c r="M4" s="4">
+        <v>1149</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1499</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="E5" s="4">
+        <v>929</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1659</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1349</v>
+      </c>
+      <c r="K5" s="4">
+        <v>2579</v>
+      </c>
+      <c r="M5" s="4">
+        <v>2299</v>
+      </c>
+      <c r="O5" s="4">
+        <v>2999</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1">
-        <v>69</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1">
-        <v>99</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1">
-        <v>149</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1">
-        <v>205</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1">
-        <v>295</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1">
-        <v>499</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1">
-        <v>469</v>
-      </c>
-      <c r="E4" s="1">
-        <v>689</v>
-      </c>
-      <c r="F4" s="1">
-        <v>679</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1159</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1149</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1369</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1">
-        <v>1649</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1">
-        <v>929</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1369</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1349</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2299</v>
-      </c>
-      <c r="H5" s="1">
-        <v>2299</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2729</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1">
-        <v>3249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="E6" s="4">
         <v>1999</v>
       </c>
-      <c r="E6" s="1">
-        <v>2899</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="G6" s="4">
+        <v>3549</v>
+      </c>
+      <c r="I6" s="4">
         <v>2849</v>
       </c>
-      <c r="G6" s="1">
+      <c r="K6" s="4">
+        <v>5449</v>
+      </c>
+      <c r="M6" s="4">
         <v>4849</v>
       </c>
-      <c r="H6" s="1">
-        <v>4849</v>
-      </c>
-      <c r="I6" s="1">
-        <v>5749</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1">
-        <v>6499</v>
+      <c r="O6" s="4">
+        <v>6349</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>6999</v>
       </c>
     </row>
   </sheetData>
